--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdOutRightRepoTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdOutRightRepoTrade001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Workspace\workspace-2.0.1.1-idea\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C748A1C3-BEF5-4B89-857B-C08F6BE28711}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>业务编号</t>
   </si>
@@ -81,13 +80,17 @@
   </si>
   <si>
     <t>标的资产名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -153,7 +156,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -228,23 +231,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -280,23 +266,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -472,14 +441,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="18" width="15.59765625" customWidth="1"/>
+    <col min="1" max="19" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -501,37 +470,40 @@
       <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>6</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdOutRightRepoTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdOutRightRepoTrade001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>业务编号</t>
   </si>
@@ -80,10 +80,6 @@
   </si>
   <si>
     <t>标的资产名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -442,13 +438,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="19" width="15.625" customWidth="1"/>
+    <col min="1" max="18" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -470,40 +466,37 @@
       <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>18</v>
+      <c r="H1" t="s">
+        <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" t="s">
         <v>7</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>6</v>
+      </c>
       <c r="R1" t="s">
-        <v>6</v>
-      </c>
-      <c r="S1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdOutRightRepoTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdOutRightRepoTrade001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workSpaceGZNEW\tams\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440"/>
+    <workbookView xWindow="28680" yWindow="-50" windowWidth="29040" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>标的资产名称</t>
+    <t>资产简称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -439,12 +439,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="18" width="15.625" customWidth="1"/>
+    <col min="1" max="18" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
